--- a/DataRepo/tests/data/small_obob/small_obob_animal_and_sample_table_blank_sample.xlsx
+++ b/DataRepo/tests/data/small_obob/small_obob_animal_and_sample_table_blank_sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/data/tests/small_obob/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/tests/data/small_obob/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D910AC8D-86CA-B44F-92EB-9BF9E7ECEB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4506DA-8458-1842-9A97-860024B8B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="500" windowWidth="28800" windowHeight="16480" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="600" windowWidth="28800" windowHeight="16480" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Study" sheetId="9" r:id="rId1"/>
@@ -2777,9 +2777,6 @@
     <t>small_obob_maven_6eaas_inf_blank_sample.xlsx</t>
   </si>
   <si>
-    <t>DataRepo/data/tests/small_obob/small_obob_maven_6eaas_inf_blank_sample.xlsx</t>
-  </si>
-  <si>
     <t>2021-04-29</t>
   </si>
   <si>
@@ -2787,6 +2784,9 @@
   </si>
   <si>
     <t>Michael Neinast, polar-HILIC-25-min, unknown, 2021-04-29</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/small_obob/small_obob_maven_6eaas_inf_blank_sample.xlsx</t>
   </si>
 </sst>
 </file>
@@ -27583,10 +27583,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C2" t="s">
         <v>128</v>
@@ -27595,7 +27595,7 @@
         <v>129</v>
       </c>
       <c r="E2" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -27642,13 +27642,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="20" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B2" s="20" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -27700,7 +27700,7 @@
         <v>348</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -27714,7 +27714,7 @@
         <v>348</v>
       </c>
       <c r="E3" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -27728,7 +27728,7 @@
         <v>348</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -27742,7 +27742,7 @@
         <v>348</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -27756,7 +27756,7 @@
         <v>348</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -27770,7 +27770,7 @@
         <v>348</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -27784,7 +27784,7 @@
         <v>348</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -27798,7 +27798,7 @@
         <v>348</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -27812,7 +27812,7 @@
         <v>348</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -27826,7 +27826,7 @@
         <v>348</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -27840,7 +27840,7 @@
         <v>348</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -27854,7 +27854,7 @@
         <v>348</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -27868,7 +27868,7 @@
         <v>348</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -27882,7 +27882,7 @@
         <v>348</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -27896,7 +27896,7 @@
         <v>348</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F16" s="20" t="s">
         <v>347</v>
